--- a/slides/03-ADaM/metadata/posit_specs.xlsx
+++ b/slides/03-ADaM/metadata/posit_specs.xlsx
@@ -1,28 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rpharma-2024-ADaM-workshop\metadata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1816FBBB-1CCF-4C27-88B0-6D62188DD366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4157" yWindow="0" windowWidth="19562" windowHeight="10257" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4157" yWindow="0" windowWidth="19562" windowHeight="10257" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Study" sheetId="1" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="Variables" sheetId="12" r:id="rId3"/>
-    <sheet name="ValueLevel" sheetId="4" r:id="rId4"/>
-    <sheet name="WhereClauses" sheetId="15" r:id="rId5"/>
-    <sheet name="Codelists" sheetId="13" r:id="rId6"/>
-    <sheet name="Dictionaries" sheetId="6" r:id="rId7"/>
-    <sheet name="Methods" sheetId="14" r:id="rId8"/>
-    <sheet name="Comments" sheetId="8" r:id="rId9"/>
-    <sheet name="Documents" sheetId="9" r:id="rId10"/>
+    <sheet name="Study" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Variables" sheetId="12" state="visible" r:id="rId3"/>
+    <sheet name="ValueLevel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="WhereClauses" sheetId="15" state="visible" r:id="rId5"/>
+    <sheet name="Codelists" sheetId="13" state="visible" r:id="rId6"/>
+    <sheet name="Dictionaries" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Methods" sheetId="14" state="visible" r:id="rId8"/>
+    <sheet name="Comments" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Documents" sheetId="9" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Comments!$A$1:$D$60</definedName>
@@ -34,27 +27,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Variables!$A$1:$S$118</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
   <si>
     <t>Attribute</t>
   </si>
@@ -1912,7 +1889,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1924,24 +1902,12 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1950,15 +1916,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1991,50 +1955,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2348,15 +2306,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="74.25" customWidth="1"/>
+    <col min="1" max="1" width="19.375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="74.25" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2364,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2372,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2380,7 +2338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2388,7 +2346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2396,31 +2354,32 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="62.375" customWidth="1"/>
-    <col min="3" max="3" width="19.375" customWidth="1"/>
+    <col min="1" max="1" width="19.375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="62.375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
@@ -2431,7 +2390,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>595</v>
       </c>
@@ -2445,25 +2404,27 @@
   </sheetData>
   <autoFilter ref="A1:C2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="50.75" customWidth="1"/>
-    <col min="5" max="5" width="58.625" customWidth="1"/>
-    <col min="6" max="6" width="12.375" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
-    <col min="8" max="9" width="19.375" customWidth="1"/>
+    <col min="1" max="1" width="11.75" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="50.75" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="58.625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12.375" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.375" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="19.375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2492,7 +2453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2515,7 +2476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -2541,36 +2502,37 @@
   </sheetData>
   <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129AE431-5806-471D-9C82-A144A32316F7}">
-  <dimension ref="A1:S118"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="32.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="35.125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.75" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.75" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="15.25" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.75" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="10.75" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="8" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="15.125" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="14.625" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="32.25" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="14.375" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="17.375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1">
+      <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2585,7 +2547,7 @@
       <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -2628,8 +2590,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2644,13 +2606,13 @@
       <c r="E2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>49</v>
+      <c r="F2" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="3"/>
+      <c r="L2" s="2"/>
       <c r="M2" t="s">
         <v>44</v>
       </c>
@@ -2658,8 +2620,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="3">
+      <c r="A3" s="13" t="n">
         <f t="shared" ref="A3:A62" si="0">A2+1</f>
         <v>2</v>
       </c>
@@ -2675,13 +2637,13 @@
       <c r="E3" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
       <c r="M3" t="s">
         <v>44</v>
       </c>
@@ -2692,8 +2654,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4">
+      <c r="A4" s="13" t="n">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2709,13 +2671,13 @@
       <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="2"/>
       <c r="M4" t="s">
         <v>44</v>
       </c>
@@ -2726,8 +2688,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5">
+      <c r="A5" s="13" t="n">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2743,13 +2705,13 @@
       <c r="E5" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="2"/>
       <c r="M5" t="s">
         <v>44</v>
       </c>
@@ -2757,8 +2719,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row r="6">
+      <c r="A6" s="13" t="n">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2774,13 +2736,13 @@
       <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="2"/>
       <c r="M6" t="s">
         <v>44</v>
       </c>
@@ -2788,8 +2750,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+    <row r="7">
+      <c r="A7" s="13" t="n">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2805,7 +2767,7 @@
       <c r="E7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6" t="n">
         <v>10</v>
       </c>
       <c r="I7" t="s">
@@ -2814,13 +2776,13 @@
       <c r="K7" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="2"/>
       <c r="M7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="8">
+      <c r="A8" s="13" t="n">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2836,7 +2798,7 @@
       <c r="E8" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="s">
@@ -2845,13 +2807,13 @@
       <c r="K8" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="2"/>
       <c r="M8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="9">
+      <c r="A9" s="13" t="n">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2867,13 +2829,13 @@
       <c r="E9" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="2"/>
       <c r="M9" t="s">
         <v>44</v>
       </c>
@@ -2881,8 +2843,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+    <row r="10">
+      <c r="A10" s="13" t="n">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2898,7 +2860,7 @@
       <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I10" t="s">
@@ -2907,7 +2869,7 @@
       <c r="K10" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="2"/>
       <c r="M10" t="s">
         <v>44</v>
       </c>
@@ -2915,8 +2877,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+    <row r="11">
+      <c r="A11" s="13" t="n">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2932,13 +2894,13 @@
       <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="9">
-        <v>3</v>
+      <c r="F11" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="2"/>
       <c r="M11" t="s">
         <v>69</v>
       </c>
@@ -2946,8 +2908,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="12">
+      <c r="A12" s="13" t="n">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2963,22 +2925,22 @@
       <c r="E12" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="2"/>
       <c r="M12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="13">
+      <c r="A13" s="13" t="n">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2994,7 +2956,7 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I13" t="s">
@@ -3003,7 +2965,7 @@
       <c r="K13" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="2"/>
       <c r="M13" t="s">
         <v>44</v>
       </c>
@@ -3014,8 +2976,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    <row r="14">
+      <c r="A14" s="13" t="n">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3031,7 +2993,7 @@
       <c r="E14" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="6" t="s">
         <v>95</v>
       </c>
       <c r="I14" t="s">
@@ -3040,7 +3002,7 @@
       <c r="K14" t="s">
         <v>96</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="2"/>
       <c r="M14" t="s">
         <v>44</v>
       </c>
@@ -3051,8 +3013,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+    <row r="15">
+      <c r="A15" s="13" t="n">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -3068,7 +3030,7 @@
       <c r="E15" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I15" t="s">
@@ -3077,13 +3039,13 @@
       <c r="K15" t="s">
         <v>101</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="2"/>
       <c r="M15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="16">
+      <c r="A16" s="13" t="n">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3099,7 +3061,7 @@
       <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="6" t="s">
         <v>104</v>
       </c>
       <c r="I16" t="s">
@@ -3108,7 +3070,7 @@
       <c r="K16" t="s">
         <v>105</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="2"/>
       <c r="M16" t="s">
         <v>69</v>
       </c>
@@ -3116,8 +3078,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="17">
+      <c r="A17" s="13" t="n">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3133,7 +3095,7 @@
       <c r="E17" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I17" t="s">
@@ -3142,13 +3104,13 @@
       <c r="K17" t="s">
         <v>109</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="2"/>
       <c r="M17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+    <row r="18">
+      <c r="A18" s="13" t="n">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -3164,7 +3126,7 @@
       <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="6" t="s">
         <v>112</v>
       </c>
       <c r="I18" t="s">
@@ -3173,7 +3135,7 @@
       <c r="K18" t="s">
         <v>113</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="2"/>
       <c r="M18" t="s">
         <v>44</v>
       </c>
@@ -3181,8 +3143,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="19">
+      <c r="A19" s="13" t="n">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3198,7 +3160,7 @@
       <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="s">
@@ -3207,7 +3169,7 @@
       <c r="K19" t="s">
         <v>117</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="2"/>
       <c r="M19" t="s">
         <v>69</v>
       </c>
@@ -3218,8 +3180,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+    <row r="20">
+      <c r="A20" s="13" t="n">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3235,7 +3197,7 @@
       <c r="E20" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="6" t="s">
         <v>122</v>
       </c>
       <c r="I20" t="s">
@@ -3244,7 +3206,7 @@
       <c r="K20" t="s">
         <v>117</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="2"/>
       <c r="M20" t="s">
         <v>44</v>
       </c>
@@ -3252,8 +3214,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+    <row r="21">
+      <c r="A21" s="13" t="n">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3269,7 +3231,7 @@
       <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="6" t="s">
         <v>122</v>
       </c>
       <c r="I21" t="s">
@@ -3278,7 +3240,7 @@
       <c r="K21" t="s">
         <v>117</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="2"/>
       <c r="M21" t="s">
         <v>69</v>
       </c>
@@ -3289,8 +3251,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+    <row r="22">
+      <c r="A22" s="13" t="n">
         <f>A21+1</f>
         <v>21</v>
       </c>
@@ -3306,7 +3268,7 @@
       <c r="E22" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H22" t="s">
@@ -3315,7 +3277,7 @@
       <c r="I22" t="s">
         <v>25</v>
       </c>
-      <c r="L22" s="3"/>
+      <c r="L22" s="2"/>
       <c r="M22" t="s">
         <v>69</v>
       </c>
@@ -3326,8 +3288,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+    <row r="23">
+      <c r="A23" s="13" t="n">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3343,13 +3305,13 @@
       <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="2"/>
       <c r="M23" t="s">
         <v>44</v>
       </c>
@@ -3360,8 +3322,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+    <row r="24">
+      <c r="A24" s="13" t="n">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -3377,13 +3339,13 @@
       <c r="E24" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="6" t="s">
         <v>135</v>
       </c>
       <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="3"/>
+      <c r="L24" s="2"/>
       <c r="M24" t="s">
         <v>44</v>
       </c>
@@ -3394,8 +3356,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    <row r="25">
+      <c r="A25" s="13" t="n">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3411,13 +3373,13 @@
       <c r="E25" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I25" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="3"/>
+      <c r="L25" s="2"/>
       <c r="M25" t="s">
         <v>44</v>
       </c>
@@ -3428,8 +3390,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    <row r="26">
+      <c r="A26" s="13" t="n">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3445,13 +3407,13 @@
       <c r="E26" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="6" t="s">
         <v>135</v>
       </c>
       <c r="I26" t="s">
         <v>24</v>
       </c>
-      <c r="L26" s="3"/>
+      <c r="L26" s="2"/>
       <c r="M26" t="s">
         <v>44</v>
       </c>
@@ -3462,8 +3424,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+    <row r="27">
+      <c r="A27" s="13" t="n">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -3479,7 +3441,7 @@
       <c r="E27" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I27" t="s">
@@ -3488,7 +3450,7 @@
       <c r="K27" t="s">
         <v>146</v>
       </c>
-      <c r="L27" s="3"/>
+      <c r="L27" s="2"/>
       <c r="M27" t="s">
         <v>69</v>
       </c>
@@ -3499,8 +3461,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+    <row r="28">
+      <c r="A28" s="13" t="n">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3516,7 +3478,7 @@
       <c r="E28" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I28" t="s">
@@ -3525,7 +3487,7 @@
       <c r="K28" t="s">
         <v>150</v>
       </c>
-      <c r="L28" s="3"/>
+      <c r="L28" s="2"/>
       <c r="M28" t="s">
         <v>74</v>
       </c>
@@ -3533,8 +3495,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+    <row r="29">
+      <c r="A29" s="13" t="n">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -3550,7 +3512,7 @@
       <c r="E29" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="6" t="s">
         <v>131</v>
       </c>
       <c r="I29" t="s">
@@ -3559,7 +3521,7 @@
       <c r="K29" t="s">
         <v>146</v>
       </c>
-      <c r="L29" s="3"/>
+      <c r="L29" s="2"/>
       <c r="M29" t="s">
         <v>69</v>
       </c>
@@ -3567,8 +3529,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+    <row r="30">
+      <c r="A30" s="13" t="n">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -3584,7 +3546,7 @@
       <c r="E30" t="s">
         <v>72</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I30" t="s">
@@ -3593,13 +3555,13 @@
       <c r="K30" t="s">
         <v>150</v>
       </c>
-      <c r="L30" s="3"/>
+      <c r="L30" s="2"/>
       <c r="M30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+    <row r="31">
+      <c r="A31" s="13" t="n">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3615,7 +3577,7 @@
       <c r="E31" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="6" t="n">
         <v>8</v>
       </c>
       <c r="H31" t="s">
@@ -3624,7 +3586,7 @@
       <c r="I31" t="s">
         <v>25</v>
       </c>
-      <c r="L31" s="3"/>
+      <c r="L31" s="2"/>
       <c r="M31" t="s">
         <v>69</v>
       </c>
@@ -3632,8 +3594,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+    <row r="32">
+      <c r="A32" s="13" t="n">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -3649,7 +3611,7 @@
       <c r="E32" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="13" t="n">
         <v>8</v>
       </c>
       <c r="H32" t="s">
@@ -3658,7 +3620,7 @@
       <c r="I32" t="s">
         <v>25</v>
       </c>
-      <c r="L32" s="3"/>
+      <c r="L32" s="2"/>
       <c r="M32" t="s">
         <v>69</v>
       </c>
@@ -3666,8 +3628,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+    <row r="33">
+      <c r="A33" s="13" t="n">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -3683,7 +3645,7 @@
       <c r="E33" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="13" t="n">
         <v>8</v>
       </c>
       <c r="H33" t="s">
@@ -3692,7 +3654,7 @@
       <c r="I33" t="s">
         <v>25</v>
       </c>
-      <c r="L33" s="3"/>
+      <c r="L33" s="2"/>
       <c r="M33" t="s">
         <v>69</v>
       </c>
@@ -3700,8 +3662,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+    <row r="34">
+      <c r="A34" s="13" t="n">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -3717,13 +3679,13 @@
       <c r="E34" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
       </c>
-      <c r="L34" s="3"/>
+      <c r="L34" s="2"/>
       <c r="M34" t="s">
         <v>69</v>
       </c>
@@ -3731,8 +3693,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+    <row r="35">
+      <c r="A35" s="13" t="n">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -3748,7 +3710,7 @@
       <c r="E35" t="s">
         <v>72</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H35" t="s">
@@ -3757,7 +3719,7 @@
       <c r="I35" t="s">
         <v>25</v>
       </c>
-      <c r="L35" s="3"/>
+      <c r="L35" s="2"/>
       <c r="M35" t="s">
         <v>69</v>
       </c>
@@ -3765,8 +3727,8 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="36">
+      <c r="A36" s="13" t="n">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -3782,7 +3744,7 @@
       <c r="E36" t="s">
         <v>72</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H36" t="s">
@@ -3791,7 +3753,7 @@
       <c r="I36" t="s">
         <v>25</v>
       </c>
-      <c r="L36" s="3"/>
+      <c r="L36" s="2"/>
       <c r="M36" t="s">
         <v>69</v>
       </c>
@@ -3799,8 +3761,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+    <row r="37">
+      <c r="A37" s="13" t="n">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -3816,13 +3778,13 @@
       <c r="E37" t="s">
         <v>48</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
       </c>
-      <c r="L37" s="3"/>
+      <c r="L37" s="2"/>
       <c r="M37" t="s">
         <v>69</v>
       </c>
@@ -3830,8 +3792,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+    <row r="38">
+      <c r="A38" s="13" t="n">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -3847,13 +3809,13 @@
       <c r="E38" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="3"/>
+      <c r="L38" s="2"/>
       <c r="M38" t="s">
         <v>69</v>
       </c>
@@ -3861,8 +3823,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+    <row r="39">
+      <c r="A39" s="13" t="n">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -3878,7 +3840,7 @@
       <c r="E39" t="s">
         <v>72</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H39" t="s">
@@ -3887,7 +3849,7 @@
       <c r="I39" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="3"/>
+      <c r="L39" s="2"/>
       <c r="M39" t="s">
         <v>69</v>
       </c>
@@ -3895,8 +3857,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+    <row r="40">
+      <c r="A40" s="13" t="n">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -3912,7 +3874,7 @@
       <c r="E40" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="6" t="s">
         <v>122</v>
       </c>
       <c r="I40" t="s">
@@ -3921,7 +3883,7 @@
       <c r="K40" t="s">
         <v>186</v>
       </c>
-      <c r="L40" s="3"/>
+      <c r="L40" s="2"/>
       <c r="M40" t="s">
         <v>44</v>
       </c>
@@ -3929,8 +3891,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="41">
+      <c r="A41" s="13" t="n">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -3946,13 +3908,13 @@
       <c r="E41" t="s">
         <v>72</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I41" t="s">
         <v>25</v>
       </c>
-      <c r="L41" s="3"/>
+      <c r="L41" s="2"/>
       <c r="M41" t="s">
         <v>69</v>
       </c>
@@ -3960,8 +3922,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="42">
+      <c r="A42" s="13" t="n">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -3977,13 +3939,13 @@
       <c r="E42" t="s">
         <v>72</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
       </c>
-      <c r="L42" s="3"/>
+      <c r="L42" s="2"/>
       <c r="M42" t="s">
         <v>69</v>
       </c>
@@ -3991,8 +3953,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="43">
+      <c r="A43" s="13" t="n">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -4008,13 +3970,13 @@
       <c r="E43" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I43" t="s">
         <v>25</v>
       </c>
-      <c r="L43" s="3"/>
+      <c r="L43" s="2"/>
       <c r="M43" t="s">
         <v>69</v>
       </c>
@@ -4022,8 +3984,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+    <row r="44">
+      <c r="A44" s="13" t="n">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -4039,13 +4001,13 @@
       <c r="E44" t="s">
         <v>48</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I44" t="s">
         <v>25</v>
       </c>
-      <c r="L44" s="3"/>
+      <c r="L44" s="2"/>
       <c r="M44" t="s">
         <v>69</v>
       </c>
@@ -4053,8 +4015,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+    <row r="45">
+      <c r="A45" s="13" t="n">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -4070,13 +4032,13 @@
       <c r="E45" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I45" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="3"/>
+      <c r="L45" s="2"/>
       <c r="M45" t="s">
         <v>69</v>
       </c>
@@ -4084,8 +4046,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="46">
+      <c r="A46" s="13" t="n">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -4101,7 +4063,7 @@
       <c r="E46" t="s">
         <v>72</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H46" t="s">
@@ -4117,8 +4079,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+    <row r="47">
+      <c r="A47" s="13" t="n">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -4134,7 +4096,7 @@
       <c r="E47" t="s">
         <v>72</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H47" t="s">
@@ -4150,8 +4112,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+    <row r="48">
+      <c r="A48" s="13" t="n">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -4167,7 +4129,7 @@
       <c r="E48" t="s">
         <v>48</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I48" t="s">
@@ -4180,8 +4142,8 @@
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+    <row r="49">
+      <c r="A49" s="13" t="n">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -4197,7 +4159,7 @@
       <c r="E49" t="s">
         <v>72</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="6" t="s">
         <v>100</v>
       </c>
       <c r="H49" t="s">
@@ -4213,8 +4175,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+    <row r="50">
+      <c r="A50" s="13" t="n">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -4230,7 +4192,7 @@
       <c r="E50" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I50" t="s">
@@ -4243,8 +4205,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+    <row r="51">
+      <c r="A51" s="13" t="n">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -4260,7 +4222,7 @@
       <c r="E51" t="s">
         <v>48</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="7" t="s">
         <v>216</v>
       </c>
       <c r="I51" t="s">
@@ -4273,8 +4235,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+    <row r="52">
+      <c r="A52" s="13" t="n">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -4290,7 +4252,7 @@
       <c r="E52" t="s">
         <v>48</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="7" t="s">
         <v>216</v>
       </c>
       <c r="I52" t="s">
@@ -4303,8 +4265,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+    <row r="53">
+      <c r="A53" s="13" t="n">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -4320,7 +4282,7 @@
       <c r="E53" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="6" t="n">
         <v>20</v>
       </c>
       <c r="I53" t="s">
@@ -4333,8 +4295,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+    <row r="54">
+      <c r="A54" s="13" t="n">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -4350,13 +4312,13 @@
       <c r="E54" t="s">
         <v>72</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I54" t="s">
         <v>25</v>
       </c>
-      <c r="L54" s="3"/>
+      <c r="L54" s="2"/>
       <c r="M54" t="s">
         <v>69</v>
       </c>
@@ -4364,8 +4326,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+    <row r="55">
+      <c r="A55" s="13" t="n">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -4381,7 +4343,7 @@
       <c r="E55" t="s">
         <v>48</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="7" t="s">
         <v>224</v>
       </c>
       <c r="I55" t="s">
@@ -4394,8 +4356,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+    <row r="56">
+      <c r="A56" s="13" t="n">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -4411,7 +4373,7 @@
       <c r="E56" t="s">
         <v>48</v>
       </c>
-      <c r="F56" s="10" t="s">
+      <c r="F56" s="7" t="s">
         <v>226</v>
       </c>
       <c r="I56" t="s">
@@ -4424,8 +4386,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+    <row r="57">
+      <c r="A57" s="13" t="n">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -4441,7 +4403,7 @@
       <c r="E57" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="10" t="s">
+      <c r="F57" s="7" t="s">
         <v>224</v>
       </c>
       <c r="I57" t="s">
@@ -4454,8 +4416,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+    <row r="58">
+      <c r="A58" s="13" t="n">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -4471,7 +4433,7 @@
       <c r="E58" t="s">
         <v>72</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I58" t="s">
@@ -4484,8 +4446,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+    <row r="59">
+      <c r="A59" s="13" t="n">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -4501,7 +4463,7 @@
       <c r="E59" t="s">
         <v>48</v>
       </c>
-      <c r="F59" s="10" t="s">
+      <c r="F59" s="7" t="s">
         <v>49</v>
       </c>
       <c r="I59" t="s">
@@ -4514,8 +4476,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+    <row r="60">
+      <c r="A60" s="13" t="n">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -4531,7 +4493,7 @@
       <c r="E60" t="s">
         <v>48</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F60" s="7" t="s">
         <v>49</v>
       </c>
       <c r="I60" t="s">
@@ -4540,7 +4502,7 @@
       <c r="K60" t="s">
         <v>90</v>
       </c>
-      <c r="L60" s="3"/>
+      <c r="L60" s="2"/>
       <c r="M60" t="s">
         <v>44</v>
       </c>
@@ -4548,8 +4510,8 @@
         <v>231</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+    <row r="61">
+      <c r="A61" s="13" t="n">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -4565,7 +4527,7 @@
       <c r="E61" t="s">
         <v>48</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="7" t="s">
         <v>95</v>
       </c>
       <c r="I61" t="s">
@@ -4574,7 +4536,7 @@
       <c r="K61" t="s">
         <v>96</v>
       </c>
-      <c r="L61" s="3"/>
+      <c r="L61" s="2"/>
       <c r="M61" t="s">
         <v>44</v>
       </c>
@@ -4582,8 +4544,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+    <row r="62">
+      <c r="A62" s="13" t="n">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -4599,7 +4561,7 @@
       <c r="E62" t="s">
         <v>48</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="13" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="s">
@@ -4608,7 +4570,7 @@
       <c r="K62" t="s">
         <v>117</v>
       </c>
-      <c r="L62" s="3"/>
+      <c r="L62" s="2"/>
       <c r="M62" t="s">
         <v>44</v>
       </c>
@@ -4616,8 +4578,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
+    <row r="63">
+      <c r="A63" s="13" t="n">
         <f t="shared" ref="A63:A118" si="1">A62+1</f>
         <v>62</v>
       </c>
@@ -4633,7 +4595,7 @@
       <c r="E63" t="s">
         <v>48</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="7" t="s">
         <v>131</v>
       </c>
       <c r="I63" t="s">
@@ -4642,7 +4604,7 @@
       <c r="K63" t="s">
         <v>146</v>
       </c>
-      <c r="L63" s="3"/>
+      <c r="L63" s="2"/>
       <c r="M63" t="s">
         <v>44</v>
       </c>
@@ -4650,8 +4612,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+    <row r="64">
+      <c r="A64" s="13" t="n">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -4667,7 +4629,7 @@
       <c r="E64" t="s">
         <v>48</v>
       </c>
-      <c r="F64" s="10" t="s">
+      <c r="F64" s="7" t="s">
         <v>131</v>
       </c>
       <c r="I64" t="s">
@@ -4676,7 +4638,7 @@
       <c r="K64" t="s">
         <v>146</v>
       </c>
-      <c r="L64" s="3"/>
+      <c r="L64" s="2"/>
       <c r="M64" t="s">
         <v>44</v>
       </c>
@@ -4684,8 +4646,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
+    <row r="65">
+      <c r="A65" s="13" t="n">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -4701,7 +4663,7 @@
       <c r="E65" t="s">
         <v>72</v>
       </c>
-      <c r="F65" s="10" t="s">
+      <c r="F65" s="7" t="s">
         <v>100</v>
       </c>
       <c r="H65" t="s">
@@ -4710,7 +4672,7 @@
       <c r="I65" t="s">
         <v>25</v>
       </c>
-      <c r="L65" s="3"/>
+      <c r="L65" s="2"/>
       <c r="M65" t="s">
         <v>44</v>
       </c>
@@ -4718,8 +4680,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
+    <row r="66">
+      <c r="A66" s="13" t="n">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
@@ -4735,7 +4697,7 @@
       <c r="E66" t="s">
         <v>72</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="13" t="n">
         <v>8</v>
       </c>
       <c r="H66" t="s">
@@ -4744,7 +4706,7 @@
       <c r="I66" t="s">
         <v>25</v>
       </c>
-      <c r="L66" s="3"/>
+      <c r="L66" s="2"/>
       <c r="M66" t="s">
         <v>44</v>
       </c>
@@ -4752,8 +4714,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+    <row r="67">
+      <c r="A67" s="13" t="n">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
@@ -4769,7 +4731,7 @@
       <c r="E67" t="s">
         <v>72</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="7" t="s">
         <v>100</v>
       </c>
       <c r="H67" t="s">
@@ -4778,7 +4740,7 @@
       <c r="I67" t="s">
         <v>25</v>
       </c>
-      <c r="L67" s="3"/>
+      <c r="L67" s="2"/>
       <c r="M67" t="s">
         <v>44</v>
       </c>
@@ -4786,8 +4748,8 @@
         <v>171</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
+    <row r="68">
+      <c r="A68" s="13" t="n">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -4803,13 +4765,13 @@
       <c r="E68" t="s">
         <v>48</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I68" t="s">
         <v>25</v>
       </c>
-      <c r="L68" s="3"/>
+      <c r="L68" s="2"/>
       <c r="M68" t="s">
         <v>44</v>
       </c>
@@ -4817,8 +4779,8 @@
         <v>236</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
+    <row r="69">
+      <c r="A69" s="13" t="n">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -4834,13 +4796,13 @@
       <c r="E69" t="s">
         <v>48</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I69" t="s">
         <v>25</v>
       </c>
-      <c r="L69" s="3"/>
+      <c r="L69" s="2"/>
       <c r="M69" t="s">
         <v>44</v>
       </c>
@@ -4848,8 +4810,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
+    <row r="70">
+      <c r="A70" s="13" t="n">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -4865,13 +4827,13 @@
       <c r="E70" t="s">
         <v>48</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I70" t="s">
         <v>25</v>
       </c>
-      <c r="L70" s="3"/>
+      <c r="L70" s="2"/>
       <c r="M70" t="s">
         <v>44</v>
       </c>
@@ -4879,8 +4841,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="4">
+    <row r="71">
+      <c r="A71" s="13" t="n">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -4896,13 +4858,13 @@
       <c r="E71" t="s">
         <v>48</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="6" t="n">
         <v>100</v>
       </c>
       <c r="I71" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="3"/>
+      <c r="L71" s="2"/>
       <c r="M71" t="s">
         <v>44</v>
       </c>
@@ -4910,8 +4872,8 @@
         <v>245</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+    <row r="72">
+      <c r="A72" s="13" t="n">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
@@ -4927,13 +4889,13 @@
       <c r="E72" t="s">
         <v>48</v>
       </c>
-      <c r="F72" s="9">
+      <c r="F72" s="6" t="n">
         <v>200</v>
       </c>
       <c r="I72" t="s">
         <v>25</v>
       </c>
-      <c r="L72" s="3"/>
+      <c r="L72" s="2"/>
       <c r="M72" t="s">
         <v>44</v>
       </c>
@@ -4941,8 +4903,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
+    <row r="73">
+      <c r="A73" s="13" t="n">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
@@ -4958,13 +4920,13 @@
       <c r="E73" t="s">
         <v>48</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I73" t="s">
         <v>25</v>
       </c>
-      <c r="L73" s="3"/>
+      <c r="L73" s="2"/>
       <c r="M73" t="s">
         <v>44</v>
       </c>
@@ -4972,8 +4934,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
+    <row r="74">
+      <c r="A74" s="13" t="n">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
@@ -4989,13 +4951,13 @@
       <c r="E74" t="s">
         <v>48</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="6" t="n">
         <v>200</v>
       </c>
       <c r="I74" t="s">
         <v>25</v>
       </c>
-      <c r="L74" s="3"/>
+      <c r="L74" s="2"/>
       <c r="M74" t="s">
         <v>44</v>
       </c>
@@ -5003,8 +4965,8 @@
         <v>254</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
+    <row r="75">
+      <c r="A75" s="13" t="n">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
@@ -5020,13 +4982,13 @@
       <c r="E75" t="s">
         <v>257</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I75" t="s">
         <v>25</v>
       </c>
-      <c r="L75" s="3"/>
+      <c r="L75" s="2"/>
       <c r="M75" t="s">
         <v>44</v>
       </c>
@@ -5034,8 +4996,8 @@
         <v>258</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="4">
+    <row r="76">
+      <c r="A76" s="13" t="n">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
@@ -5051,13 +5013,13 @@
       <c r="E76" t="s">
         <v>48</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I76" t="s">
         <v>25</v>
       </c>
-      <c r="L76" s="3"/>
+      <c r="L76" s="2"/>
       <c r="M76" t="s">
         <v>44</v>
       </c>
@@ -5065,8 +5027,8 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="4">
+    <row r="77">
+      <c r="A77" s="13" t="n">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
@@ -5082,13 +5044,13 @@
       <c r="E77" t="s">
         <v>48</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I77" t="s">
         <v>25</v>
       </c>
-      <c r="L77" s="3"/>
+      <c r="L77" s="2"/>
       <c r="M77" t="s">
         <v>44</v>
       </c>
@@ -5096,8 +5058,8 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="4">
+    <row r="78">
+      <c r="A78" s="13" t="n">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
@@ -5113,57 +5075,57 @@
       <c r="E78" t="s">
         <v>48</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="6" t="n">
         <v>200</v>
       </c>
       <c r="I78" t="s">
         <v>25</v>
       </c>
-      <c r="L78" s="3"/>
+      <c r="L78" s="2"/>
       <c r="M78" t="s">
         <v>44</v>
       </c>
-      <c r="P78" t="s">
+      <c r="P78" s="10" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="79" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="17">
+    <row r="79">
+      <c r="A79" s="9" t="n">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D79" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="E79" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F79" s="19" t="s">
+      <c r="E79" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="I79" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L79" s="20"/>
-      <c r="M79" s="18" t="s">
+      <c r="L79" s="12"/>
+      <c r="M79" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P79" s="18" t="s">
+      <c r="P79" s="10" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="4">
+    <row r="80">
+      <c r="A80" s="13" t="n">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C80" t="s">
@@ -5175,13 +5137,13 @@
       <c r="E80" t="s">
         <v>72</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I80" t="s">
         <v>25</v>
       </c>
-      <c r="L80" s="3"/>
+      <c r="L80" s="2"/>
       <c r="M80" t="s">
         <v>44</v>
       </c>
@@ -5189,12 +5151,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="4">
+    <row r="81">
+      <c r="A81" s="13" t="n">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C81" t="s">
@@ -5206,13 +5168,13 @@
       <c r="E81" t="s">
         <v>48</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="6" t="n">
         <v>200</v>
       </c>
       <c r="I81" t="s">
         <v>25</v>
       </c>
-      <c r="L81" s="3"/>
+      <c r="L81" s="2"/>
       <c r="M81" t="s">
         <v>44</v>
       </c>
@@ -5220,12 +5182,12 @@
         <v>276</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
+    <row r="82">
+      <c r="A82" s="13" t="n">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C82" t="s">
@@ -5237,13 +5199,13 @@
       <c r="E82" t="s">
         <v>279</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="6" t="n">
         <v>25</v>
       </c>
       <c r="I82" t="s">
         <v>25</v>
       </c>
-      <c r="L82" s="3"/>
+      <c r="L82" s="2"/>
       <c r="M82" t="s">
         <v>44</v>
       </c>
@@ -5251,12 +5213,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="4">
+    <row r="83">
+      <c r="A83" s="13" t="n">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C83" t="s">
@@ -5268,13 +5230,13 @@
       <c r="E83" t="s">
         <v>72</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I83" t="s">
         <v>25</v>
       </c>
-      <c r="L83" s="3"/>
+      <c r="L83" s="2"/>
       <c r="M83" t="s">
         <v>44</v>
       </c>
@@ -5282,12 +5244,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="4">
+    <row r="84">
+      <c r="A84" s="13" t="n">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C84" t="s">
@@ -5299,13 +5261,13 @@
       <c r="E84" t="s">
         <v>48</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I84" t="s">
         <v>25</v>
       </c>
-      <c r="L84" s="3"/>
+      <c r="L84" s="2"/>
       <c r="M84" t="s">
         <v>44</v>
       </c>
@@ -5313,12 +5275,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="4">
+    <row r="85">
+      <c r="A85" s="13" t="n">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C85" t="s">
@@ -5330,13 +5292,13 @@
       <c r="E85" t="s">
         <v>72</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I85" t="s">
         <v>25</v>
       </c>
-      <c r="L85" s="3"/>
+      <c r="L85" s="2"/>
       <c r="M85" t="s">
         <v>44</v>
       </c>
@@ -5344,12 +5306,12 @@
         <v>289</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="4">
+    <row r="86">
+      <c r="A86" s="13" t="n">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C86" t="s">
@@ -5361,13 +5323,13 @@
       <c r="E86" t="s">
         <v>48</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="6" t="n">
         <v>40</v>
       </c>
       <c r="I86" t="s">
         <v>25</v>
       </c>
-      <c r="L86" s="3"/>
+      <c r="L86" s="2"/>
       <c r="M86" t="s">
         <v>44</v>
       </c>
@@ -5375,12 +5337,12 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="4">
+    <row r="87">
+      <c r="A87" s="13" t="n">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C87" t="s">
@@ -5392,13 +5354,13 @@
       <c r="E87" t="s">
         <v>72</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I87" t="s">
         <v>25</v>
       </c>
-      <c r="L87" s="3"/>
+      <c r="L87" s="2"/>
       <c r="M87" t="s">
         <v>44</v>
       </c>
@@ -5406,12 +5368,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
+    <row r="88">
+      <c r="A88" s="13" t="n">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C88" t="s">
@@ -5423,13 +5385,13 @@
       <c r="E88" t="s">
         <v>72</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I88" t="s">
         <v>25</v>
       </c>
-      <c r="L88" s="3"/>
+      <c r="L88" s="2"/>
       <c r="M88" t="s">
         <v>44</v>
       </c>
@@ -5437,12 +5399,12 @@
         <v>298</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="4">
+    <row r="89">
+      <c r="A89" s="13" t="n">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C89" t="s">
@@ -5454,13 +5416,13 @@
       <c r="E89" t="s">
         <v>48</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I89" t="s">
         <v>25</v>
       </c>
-      <c r="L89" s="3"/>
+      <c r="L89" s="2"/>
       <c r="M89" t="s">
         <v>44</v>
       </c>
@@ -5468,12 +5430,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
+    <row r="90">
+      <c r="A90" s="13" t="n">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C90" t="s">
@@ -5485,7 +5447,7 @@
       <c r="E90" t="s">
         <v>48</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="6" t="n">
         <v>200</v>
       </c>
       <c r="I90" t="s">
@@ -5494,17 +5456,17 @@
       <c r="K90" t="s">
         <v>304</v>
       </c>
-      <c r="L90" s="3"/>
+      <c r="L90" s="2"/>
       <c r="M90" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="4">
+    <row r="91">
+      <c r="A91" s="13" t="n">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C91" t="s">
@@ -5516,7 +5478,7 @@
       <c r="E91" t="s">
         <v>72</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I91" t="s">
@@ -5525,17 +5487,17 @@
       <c r="K91" t="s">
         <v>307</v>
       </c>
-      <c r="L91" s="3"/>
+      <c r="L91" s="2"/>
       <c r="M91" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
+    <row r="92">
+      <c r="A92" s="13" t="n">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C92" t="s">
@@ -5547,7 +5509,7 @@
       <c r="E92" t="s">
         <v>48</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I92" t="s">
@@ -5556,17 +5518,17 @@
       <c r="K92" t="s">
         <v>310</v>
       </c>
-      <c r="L92" s="3"/>
+      <c r="L92" s="2"/>
       <c r="M92" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="4">
+    <row r="93">
+      <c r="A93" s="13" t="n">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C93" t="s">
@@ -5578,10 +5540,10 @@
       <c r="E93" t="s">
         <v>257</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L93" s="3"/>
+      <c r="L93" s="2"/>
       <c r="M93" t="s">
         <v>69</v>
       </c>
@@ -5589,12 +5551,12 @@
         <v>313</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
+    <row r="94">
+      <c r="A94" s="13" t="n">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C94" t="s">
@@ -5606,10 +5568,10 @@
       <c r="E94" t="s">
         <v>48</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L94" s="3"/>
+      <c r="L94" s="2"/>
       <c r="M94" t="s">
         <v>74</v>
       </c>
@@ -5617,12 +5579,12 @@
         <v>316</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="4">
+    <row r="95">
+      <c r="A95" s="13" t="n">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C95" t="s">
@@ -5634,10 +5596,10 @@
       <c r="E95" t="s">
         <v>48</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L95" s="3"/>
+      <c r="L95" s="2"/>
       <c r="M95" t="s">
         <v>69</v>
       </c>
@@ -5645,12 +5607,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
+    <row r="96">
+      <c r="A96" s="13" t="n">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C96" t="s">
@@ -5662,20 +5624,20 @@
       <c r="E96" t="s">
         <v>72</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L96" s="3"/>
+      <c r="L96" s="2"/>
       <c r="M96" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A97" s="4">
+    <row r="97">
+      <c r="A97" s="13" t="n">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C97" t="s">
@@ -5687,10 +5649,10 @@
       <c r="E97" t="s">
         <v>257</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L97" s="3"/>
+      <c r="L97" s="2"/>
       <c r="M97" t="s">
         <v>69</v>
       </c>
@@ -5698,12 +5660,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
+    <row r="98">
+      <c r="A98" s="13" t="n">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C98" t="s">
@@ -5715,10 +5677,10 @@
       <c r="E98" t="s">
         <v>48</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="L98" s="3"/>
+      <c r="L98" s="2"/>
       <c r="M98" t="s">
         <v>74</v>
       </c>
@@ -5726,12 +5688,12 @@
         <v>327</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A99" s="4">
+    <row r="99">
+      <c r="A99" s="13" t="n">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C99" t="s">
@@ -5743,13 +5705,13 @@
       <c r="E99" t="s">
         <v>48</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K99" t="s">
         <v>117</v>
       </c>
-      <c r="L99" s="3"/>
+      <c r="L99" s="2"/>
       <c r="M99" t="s">
         <v>69</v>
       </c>
@@ -5757,12 +5719,12 @@
         <v>330</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
+    <row r="100">
+      <c r="A100" s="13" t="n">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C100" t="s">
@@ -5774,10 +5736,10 @@
       <c r="E100" t="s">
         <v>257</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L100" s="3"/>
+      <c r="L100" s="2"/>
       <c r="M100" t="s">
         <v>69</v>
       </c>
@@ -5785,12 +5747,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
+    <row r="101">
+      <c r="A101" s="13" t="n">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C101" t="s">
@@ -5802,10 +5764,10 @@
       <c r="E101" t="s">
         <v>257</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L101" s="3"/>
+      <c r="L101" s="2"/>
       <c r="M101" t="s">
         <v>69</v>
       </c>
@@ -5813,12 +5775,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
+    <row r="102">
+      <c r="A102" s="13" t="n">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C102" t="s">
@@ -5830,10 +5792,10 @@
       <c r="E102" t="s">
         <v>48</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="2"/>
       <c r="M102" t="s">
         <v>69</v>
       </c>
@@ -5841,12 +5803,12 @@
         <v>339</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="4">
+    <row r="103">
+      <c r="A103" s="13" t="n">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C103" t="s">
@@ -5858,10 +5820,10 @@
       <c r="E103" t="s">
         <v>257</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L103" s="3"/>
+      <c r="L103" s="2"/>
       <c r="M103" t="s">
         <v>74</v>
       </c>
@@ -5869,12 +5831,12 @@
         <v>342</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
+    <row r="104">
+      <c r="A104" s="13" t="n">
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C104" t="s">
@@ -5886,10 +5848,10 @@
       <c r="E104" t="s">
         <v>257</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L104" s="3"/>
+      <c r="L104" s="2"/>
       <c r="M104" t="s">
         <v>74</v>
       </c>
@@ -5897,12 +5859,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
+    <row r="105">
+      <c r="A105" s="13" t="n">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
@@ -5914,10 +5876,10 @@
       <c r="E105" t="s">
         <v>48</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="L105" s="3"/>
+      <c r="L105" s="2"/>
       <c r="M105" t="s">
         <v>69</v>
       </c>
@@ -5925,12 +5887,12 @@
         <v>348</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
+    <row r="106">
+      <c r="A106" s="13" t="n">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C106" t="s">
@@ -5942,10 +5904,10 @@
       <c r="E106" t="s">
         <v>48</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="L106" s="3"/>
+      <c r="L106" s="2"/>
       <c r="M106" t="s">
         <v>69</v>
       </c>
@@ -5953,12 +5915,12 @@
         <v>351</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A107" s="4">
+    <row r="107">
+      <c r="A107" s="13" t="n">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C107" t="s">
@@ -5970,10 +5932,10 @@
       <c r="E107" t="s">
         <v>257</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L107" s="3"/>
+      <c r="L107" s="2"/>
       <c r="M107" t="s">
         <v>74</v>
       </c>
@@ -5981,12 +5943,12 @@
         <v>354</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
+    <row r="108">
+      <c r="A108" s="13" t="n">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C108" t="s">
@@ -5998,10 +5960,10 @@
       <c r="E108" t="s">
         <v>257</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L108" s="3"/>
+      <c r="L108" s="2"/>
       <c r="M108" t="s">
         <v>74</v>
       </c>
@@ -6009,12 +5971,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
+    <row r="109">
+      <c r="A109" s="13" t="n">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C109" t="s">
@@ -6026,10 +5988,10 @@
       <c r="E109" t="s">
         <v>72</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L109" s="3"/>
+      <c r="L109" s="2"/>
       <c r="M109" t="s">
         <v>69</v>
       </c>
@@ -6037,12 +5999,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
+    <row r="110">
+      <c r="A110" s="13" t="n">
         <f t="shared" si="1"/>
         <v>109</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C110" t="s">
@@ -6054,10 +6016,10 @@
       <c r="E110" t="s">
         <v>72</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L110" s="3"/>
+      <c r="L110" s="2"/>
       <c r="M110" t="s">
         <v>69</v>
       </c>
@@ -6065,12 +6027,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111" s="4">
+    <row r="111">
+      <c r="A111" s="13" t="n">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C111" t="s">
@@ -6082,10 +6044,10 @@
       <c r="E111" t="s">
         <v>48</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="L111" s="3"/>
+      <c r="L111" s="2"/>
       <c r="M111" t="s">
         <v>69</v>
       </c>
@@ -6093,12 +6055,12 @@
         <v>366</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
+    <row r="112">
+      <c r="A112" s="13" t="n">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C112" t="s">
@@ -6110,10 +6072,10 @@
       <c r="E112" t="s">
         <v>72</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L112" s="3"/>
+      <c r="L112" s="2"/>
       <c r="M112" t="s">
         <v>74</v>
       </c>
@@ -6121,12 +6083,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
+    <row r="113">
+      <c r="A113" s="13" t="n">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C113" t="s">
@@ -6138,10 +6100,10 @@
       <c r="E113" t="s">
         <v>48</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="L113" s="3"/>
+      <c r="L113" s="2"/>
       <c r="M113" t="s">
         <v>69</v>
       </c>
@@ -6149,12 +6111,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
+    <row r="114">
+      <c r="A114" s="13" t="n">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C114" t="s">
@@ -6166,10 +6128,10 @@
       <c r="E114" t="s">
         <v>72</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L114" s="3"/>
+      <c r="L114" s="2"/>
       <c r="M114" t="s">
         <v>74</v>
       </c>
@@ -6177,12 +6139,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A115" s="4">
+    <row r="115">
+      <c r="A115" s="13" t="n">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C115" t="s">
@@ -6194,10 +6156,10 @@
       <c r="E115" t="s">
         <v>48</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="L115" s="3"/>
+      <c r="L115" s="2"/>
       <c r="M115" t="s">
         <v>69</v>
       </c>
@@ -6205,12 +6167,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
+    <row r="116">
+      <c r="A116" s="13" t="n">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C116" t="s">
@@ -6222,10 +6184,10 @@
       <c r="E116" t="s">
         <v>48</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="L116" s="3"/>
+      <c r="L116" s="2"/>
       <c r="M116" t="s">
         <v>69</v>
       </c>
@@ -6233,12 +6195,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
+    <row r="117">
+      <c r="A117" s="13" t="n">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B117" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C117" t="s">
@@ -6250,13 +6212,13 @@
       <c r="E117" t="s">
         <v>48</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K117" t="s">
         <v>117</v>
       </c>
-      <c r="L117" s="3"/>
+      <c r="L117" s="2"/>
       <c r="M117" t="s">
         <v>69</v>
       </c>
@@ -6264,12 +6226,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
+    <row r="118">
+      <c r="A118" s="13" t="n">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C118" t="s">
@@ -6281,13 +6243,13 @@
       <c r="E118" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K118" t="s">
         <v>117</v>
       </c>
-      <c r="L118" s="3"/>
+      <c r="L118" s="2"/>
       <c r="M118" t="s">
         <v>69</v>
       </c>
@@ -6298,32 +6260,36 @@
   </sheetData>
   <autoFilter ref="A1:S118" xr:uid="{129AE431-5806-471D-9C82-A144A32316F7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="20.375" customWidth="1"/>
-    <col min="5" max="5" width="23.375" customWidth="1"/>
-    <col min="6" max="6" width="11.75" customWidth="1"/>
-    <col min="7" max="7" width="10.125" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11.75" customWidth="1"/>
-    <col min="11" max="11" width="16.25" customWidth="1"/>
-    <col min="12" max="13" width="12.875" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="15.25" customWidth="1"/>
-    <col min="17" max="18" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="11.75" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="18.75" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="18.75" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="23.375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.75" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.125" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.75" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="16.25" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="12.875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="11.75" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.625" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="15.25" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="15.625" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="15.625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -6382,33 +6348,34 @@
   </sheetData>
   <autoFilter ref="A1:R102" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE2FB6D-7C29-4DCD-9A90-5C2B3C20CCAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBC456A-1389-4826-89DD-7A3DE90BCF75}">
-  <dimension ref="A1:H77"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="30.375" customWidth="1"/>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
-    <col min="5" max="5" width="9" style="4"/>
-    <col min="6" max="6" width="59.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.25" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30.375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="59.75" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="62.375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
@@ -6421,10 +6388,10 @@
       <c r="D1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>392</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -6434,95 +6401,95 @@
         <v>394</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="14"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="8" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3">
+      <c r="A3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="13" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="14"/>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="8" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="4">
+      <c r="A4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="13" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="14"/>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="8" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5">
+      <c r="A5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="13" t="n">
         <v>4</v>
       </c>
       <c r="G5" s="14"/>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="8" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -6535,17 +6502,17 @@
       <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="13" t="s">
         <v>401</v>
       </c>
       <c r="G6" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -6558,17 +6525,17 @@
       <c r="D7" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="13" t="s">
         <v>404</v>
       </c>
       <c r="G7" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -6581,17 +6548,17 @@
       <c r="D8" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="13" t="s">
         <v>406</v>
       </c>
       <c r="G8" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -6604,17 +6571,17 @@
       <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="13" t="s">
         <v>409</v>
       </c>
       <c r="G9" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -6627,17 +6594,17 @@
       <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="13" t="s">
         <v>411</v>
       </c>
       <c r="G10" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -6650,17 +6617,17 @@
       <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="13" t="s">
         <v>413</v>
       </c>
       <c r="G11" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -6673,17 +6640,17 @@
       <c r="D12" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="13" t="s">
         <v>415</v>
       </c>
       <c r="G12" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -6696,14 +6663,14 @@
       <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="13" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -6713,17 +6680,17 @@
       <c r="D14" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H14" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -6733,17 +6700,17 @@
       <c r="D15" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="13" t="s">
         <v>403</v>
       </c>
       <c r="H15" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -6753,17 +6720,17 @@
       <c r="D16" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="13" t="s">
         <v>226</v>
       </c>
       <c r="H16" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -6773,17 +6740,17 @@
       <c r="D17" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="13" t="s">
         <v>418</v>
       </c>
       <c r="H17" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -6793,17 +6760,17 @@
       <c r="D18" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="13" t="s">
         <v>61</v>
       </c>
       <c r="H18" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>105</v>
       </c>
@@ -6813,14 +6780,14 @@
       <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="13" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -6830,14 +6797,14 @@
       <c r="D20" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="13" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -6847,14 +6814,14 @@
       <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>109</v>
       </c>
@@ -6864,17 +6831,17 @@
       <c r="D22" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -6884,17 +6851,17 @@
       <c r="D23" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -6904,17 +6871,17 @@
       <c r="D24" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="13" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -6924,14 +6891,14 @@
       <c r="D25" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="13" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -6941,14 +6908,14 @@
       <c r="D26" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="13" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -6958,14 +6925,14 @@
       <c r="D27" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -6975,17 +6942,17 @@
       <c r="D28" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="13" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -6995,17 +6962,17 @@
       <c r="D29" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="13" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -7015,17 +6982,17 @@
       <c r="D30" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="13" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -7038,10 +7005,10 @@
       <c r="D31" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="13" t="s">
         <v>423</v>
       </c>
       <c r="G31" t="s">
@@ -7051,7 +7018,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -7064,10 +7031,10 @@
       <c r="D32" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="13" t="s">
         <v>426</v>
       </c>
       <c r="G32" t="s">
@@ -7077,7 +7044,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -7090,10 +7057,10 @@
       <c r="D33" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="13" t="s">
         <v>429</v>
       </c>
       <c r="G33" t="s">
@@ -7103,7 +7070,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -7116,10 +7083,10 @@
       <c r="D34" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="13" t="s">
         <v>432</v>
       </c>
       <c r="G34" t="s">
@@ -7129,7 +7096,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>146</v>
       </c>
@@ -7139,14 +7106,14 @@
       <c r="D35" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="13" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>146</v>
       </c>
@@ -7156,14 +7123,14 @@
       <c r="D36" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="13" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -7173,14 +7140,14 @@
       <c r="D37" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="13" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>146</v>
       </c>
@@ -7190,14 +7157,14 @@
       <c r="D38" t="s">
         <v>48</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="13" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -7207,17 +7174,17 @@
       <c r="D39" t="s">
         <v>72</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="13" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>150</v>
       </c>
@@ -7227,17 +7194,17 @@
       <c r="D40" t="s">
         <v>72</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="13" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -7247,17 +7214,17 @@
       <c r="D41" t="s">
         <v>72</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="13" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>150</v>
       </c>
@@ -7267,17 +7234,17 @@
       <c r="D42" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="13" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>442</v>
       </c>
@@ -7290,10 +7257,10 @@
       <c r="D43" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="13" t="s">
         <v>445</v>
       </c>
       <c r="G43" t="s">
@@ -7303,7 +7270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>442</v>
       </c>
@@ -7316,10 +7283,10 @@
       <c r="D44" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="13" t="s">
         <v>420</v>
       </c>
       <c r="G44" t="s">
@@ -7329,7 +7296,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>442</v>
       </c>
@@ -7342,10 +7309,10 @@
       <c r="D45" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="13" t="s">
         <v>429</v>
       </c>
       <c r="G45" t="s">
@@ -7355,7 +7322,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>442</v>
       </c>
@@ -7368,10 +7335,10 @@
       <c r="D46" t="s">
         <v>48</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="13" t="s">
         <v>449</v>
       </c>
       <c r="G46" t="s">
@@ -7381,7 +7348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>186</v>
       </c>
@@ -7394,17 +7361,17 @@
       <c r="D47" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="13" t="s">
         <v>449</v>
       </c>
       <c r="H47" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -7414,10 +7381,10 @@
       <c r="D48" t="s">
         <v>48</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="13" t="s">
         <v>449</v>
       </c>
       <c r="G48" t="s">
@@ -7427,7 +7394,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -7437,10 +7404,10 @@
       <c r="D49" t="s">
         <v>48</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="13" t="s">
         <v>445</v>
       </c>
       <c r="G49" t="s">
@@ -7450,7 +7417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>449</v>
       </c>
@@ -7463,14 +7430,14 @@
       <c r="D50" t="s">
         <v>48</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="13" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>304</v>
       </c>
@@ -7483,20 +7450,20 @@
       <c r="D51" t="s">
         <v>48</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="13" t="s">
         <v>455</v>
       </c>
       <c r="G51" t="s">
         <v>456</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="13" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>304</v>
       </c>
@@ -7509,20 +7476,20 @@
       <c r="D52" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="13" t="s">
         <v>458</v>
       </c>
       <c r="G52" t="s">
         <v>459</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="13" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>304</v>
       </c>
@@ -7535,20 +7502,20 @@
       <c r="D53" t="s">
         <v>48</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="13" t="s">
         <v>461</v>
       </c>
       <c r="G53" t="s">
         <v>462</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="H53" s="13" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>304</v>
       </c>
@@ -7561,20 +7528,20 @@
       <c r="D54" t="s">
         <v>48</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="13" t="s">
         <v>464</v>
       </c>
       <c r="G54" t="s">
         <v>465</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="13" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>304</v>
       </c>
@@ -7587,20 +7554,20 @@
       <c r="D55" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="13" t="s">
         <v>467</v>
       </c>
       <c r="G55" t="s">
         <v>468</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="13" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>304</v>
       </c>
@@ -7613,20 +7580,20 @@
       <c r="D56" t="s">
         <v>48</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="13" t="s">
         <v>470</v>
       </c>
       <c r="G56" t="s">
         <v>471</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="13" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>304</v>
       </c>
@@ -7639,20 +7606,20 @@
       <c r="D57" t="s">
         <v>48</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="13" t="s">
         <v>474</v>
       </c>
       <c r="G57" t="s">
         <v>475</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="13" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>304</v>
       </c>
@@ -7665,20 +7632,20 @@
       <c r="D58" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="13" t="s">
         <v>477</v>
       </c>
       <c r="G58" t="s">
         <v>478</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="13" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>304</v>
       </c>
@@ -7691,20 +7658,20 @@
       <c r="D59" t="s">
         <v>48</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="13" t="s">
         <v>481</v>
       </c>
       <c r="G59" t="s">
         <v>482</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="13" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>310</v>
       </c>
@@ -7717,17 +7684,17 @@
       <c r="D60" t="s">
         <v>48</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="13" t="s">
         <v>455</v>
       </c>
       <c r="G60" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>310</v>
       </c>
@@ -7740,17 +7707,17 @@
       <c r="D61" t="s">
         <v>48</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="13" t="s">
         <v>458</v>
       </c>
       <c r="G61" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>310</v>
       </c>
@@ -7763,17 +7730,17 @@
       <c r="D62" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="13" t="s">
         <v>461</v>
       </c>
       <c r="G62" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>310</v>
       </c>
@@ -7786,17 +7753,17 @@
       <c r="D63" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="13" t="s">
         <v>464</v>
       </c>
       <c r="G63" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>310</v>
       </c>
@@ -7809,17 +7776,17 @@
       <c r="D64" t="s">
         <v>48</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="13" t="s">
         <v>467</v>
       </c>
       <c r="G64" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>310</v>
       </c>
@@ -7832,17 +7799,17 @@
       <c r="D65" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="13" t="s">
         <v>470</v>
       </c>
       <c r="G65" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>310</v>
       </c>
@@ -7855,17 +7822,17 @@
       <c r="D66" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="13" t="s">
         <v>474</v>
       </c>
       <c r="G66" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>310</v>
       </c>
@@ -7878,17 +7845,17 @@
       <c r="D67" t="s">
         <v>48</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="13" t="s">
         <v>477</v>
       </c>
       <c r="G67" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>310</v>
       </c>
@@ -7901,17 +7868,17 @@
       <c r="D68" t="s">
         <v>48</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="13" t="s">
         <v>481</v>
       </c>
       <c r="G68" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>307</v>
       </c>
@@ -7921,17 +7888,17 @@
       <c r="D69" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H69" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>307</v>
       </c>
@@ -7941,17 +7908,17 @@
       <c r="D70" t="s">
         <v>72</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="13" t="s">
         <v>403</v>
       </c>
       <c r="H70" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>307</v>
       </c>
@@ -7961,17 +7928,17 @@
       <c r="D71" t="s">
         <v>72</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="13" t="s">
         <v>226</v>
       </c>
       <c r="H71" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>307</v>
       </c>
@@ -7981,17 +7948,17 @@
       <c r="D72" t="s">
         <v>72</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="13" t="s">
         <v>418</v>
       </c>
       <c r="H72" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>307</v>
       </c>
@@ -8001,17 +7968,17 @@
       <c r="D73" t="s">
         <v>72</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="13" t="s">
         <v>61</v>
       </c>
       <c r="H73" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>307</v>
       </c>
@@ -8021,17 +7988,17 @@
       <c r="D74" t="s">
         <v>72</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H74" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>307</v>
       </c>
@@ -8041,17 +8008,17 @@
       <c r="D75" t="s">
         <v>72</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="13" t="s">
         <v>473</v>
       </c>
       <c r="H75" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>307</v>
       </c>
@@ -8061,17 +8028,17 @@
       <c r="D76" t="s">
         <v>72</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="13" t="s">
         <v>100</v>
       </c>
       <c r="H76" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>307</v>
       </c>
@@ -8081,10 +8048,10 @@
       <c r="D77" t="s">
         <v>72</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="13" t="s">
         <v>480</v>
       </c>
       <c r="H77" t="s">
@@ -8093,20 +8060,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="25.375" customWidth="1"/>
-    <col min="3" max="5" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="25.375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
@@ -8123,7 +8093,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>487</v>
       </c>
@@ -8140,7 +8110,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>490</v>
       </c>
@@ -8157,7 +8127,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>493</v>
       </c>
@@ -8177,21 +8147,22 @@
   </sheetData>
   <autoFilter ref="A1:E4" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A27F77-A36A-4B0F-AB98-73EE4727DE22}">
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="46.25" customWidth="1"/>
-    <col min="2" max="2" width="35.625" customWidth="1"/>
-    <col min="3" max="3" width="22.375" customWidth="1"/>
-    <col min="4" max="4" width="148.625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="46.25" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="35.625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22.375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="148.625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
@@ -8201,7 +8172,7 @@
       <c r="C1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="16" t="s">
         <v>497</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -8217,7 +8188,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="2" ht="28.55" customHeight="1">
       <c r="A2" t="s">
         <v>501</v>
       </c>
@@ -8227,11 +8198,11 @@
       <c r="C2" t="s">
         <v>503</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="15" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="3" ht="28.55" customHeight="1">
       <c r="A3" t="s">
         <v>505</v>
       </c>
@@ -8241,11 +8212,11 @@
       <c r="C3" t="s">
         <v>503</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="15" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>313</v>
       </c>
@@ -8255,11 +8226,11 @@
       <c r="C4" t="s">
         <v>503</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>313</v>
       </c>
@@ -8269,11 +8240,11 @@
       <c r="C5" t="s">
         <v>503</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>313</v>
       </c>
@@ -8283,11 +8254,11 @@
       <c r="C6" t="s">
         <v>503</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="17" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>313</v>
       </c>
@@ -8297,11 +8268,11 @@
       <c r="C7" t="s">
         <v>503</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="17" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>313</v>
       </c>
@@ -8311,11 +8282,11 @@
       <c r="C8" t="s">
         <v>503</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="17" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>313</v>
       </c>
@@ -8325,11 +8296,11 @@
       <c r="C9" t="s">
         <v>503</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="17" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>313</v>
       </c>
@@ -8339,11 +8310,11 @@
       <c r="C10" t="s">
         <v>503</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="17" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -8353,11 +8324,11 @@
       <c r="C11" t="s">
         <v>503</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="17" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>313</v>
       </c>
@@ -8367,11 +8338,11 @@
       <c r="C12" t="s">
         <v>503</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="17" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>316</v>
       </c>
@@ -8381,11 +8352,11 @@
       <c r="C13" t="s">
         <v>503</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="17" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="14" ht="42.8" customHeight="1">
       <c r="A14" t="s">
         <v>319</v>
       </c>
@@ -8395,11 +8366,11 @@
       <c r="C14" t="s">
         <v>503</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="17" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="26.5" x14ac:dyDescent="0.25">
+    <row r="15" ht="26.5" customHeight="1">
       <c r="A15" t="s">
         <v>324</v>
       </c>
@@ -8409,11 +8380,11 @@
       <c r="C15" t="s">
         <v>503</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="18" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="58.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="58.75" customHeight="1">
       <c r="A16" t="s">
         <v>327</v>
       </c>
@@ -8423,11 +8394,11 @@
       <c r="C16" t="s">
         <v>503</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="17" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="17" ht="42.8" customHeight="1">
       <c r="A17" t="s">
         <v>330</v>
       </c>
@@ -8437,11 +8408,11 @@
       <c r="C17" t="s">
         <v>503</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="17" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="39.4" x14ac:dyDescent="0.25">
+    <row r="18" ht="39.4" customHeight="1">
       <c r="A18" t="s">
         <v>333</v>
       </c>
@@ -8451,11 +8422,11 @@
       <c r="C18" t="s">
         <v>503</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="18" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="91.05" x14ac:dyDescent="0.25">
+    <row r="19" ht="91.05" customHeight="1">
       <c r="A19" t="s">
         <v>336</v>
       </c>
@@ -8465,11 +8436,11 @@
       <c r="C19" t="s">
         <v>503</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="18" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="20" ht="28.55" customHeight="1">
       <c r="A20" t="s">
         <v>339</v>
       </c>
@@ -8479,11 +8450,11 @@
       <c r="C20" t="s">
         <v>503</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="17" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="21" ht="57.1" customHeight="1">
       <c r="A21" t="s">
         <v>342</v>
       </c>
@@ -8493,11 +8464,11 @@
       <c r="C21" t="s">
         <v>503</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="17" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="22" ht="57.1" customHeight="1">
       <c r="A22" t="s">
         <v>345</v>
       </c>
@@ -8507,11 +8478,11 @@
       <c r="C22" t="s">
         <v>503</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="17" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="128.4" x14ac:dyDescent="0.25">
+    <row r="23" ht="128.4" customHeight="1">
       <c r="A23" t="s">
         <v>348</v>
       </c>
@@ -8521,11 +8492,11 @@
       <c r="C23" t="s">
         <v>503</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="17" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="24" ht="28.55" customHeight="1">
       <c r="A24" t="s">
         <v>351</v>
       </c>
@@ -8535,11 +8506,11 @@
       <c r="C24" t="s">
         <v>503</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="17" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="25" ht="57.1" customHeight="1">
       <c r="A25" t="s">
         <v>354</v>
       </c>
@@ -8549,11 +8520,11 @@
       <c r="C25" t="s">
         <v>503</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="17" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="26" ht="57.1" customHeight="1">
       <c r="A26" t="s">
         <v>357</v>
       </c>
@@ -8563,11 +8534,11 @@
       <c r="C26" t="s">
         <v>503</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="17" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>360</v>
       </c>
@@ -8577,11 +8548,11 @@
       <c r="C27" t="s">
         <v>503</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="18" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="42.8" x14ac:dyDescent="0.25">
+    <row r="28" ht="42.8" customHeight="1">
       <c r="A28" t="s">
         <v>363</v>
       </c>
@@ -8591,11 +8562,11 @@
       <c r="C28" t="s">
         <v>503</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="17" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>366</v>
       </c>
@@ -8605,11 +8576,11 @@
       <c r="C29" t="s">
         <v>503</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="17" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>369</v>
       </c>
@@ -8619,11 +8590,11 @@
       <c r="C30" t="s">
         <v>503</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="17" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>372</v>
       </c>
@@ -8633,11 +8604,11 @@
       <c r="C31" t="s">
         <v>503</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="17" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="32" ht="28.55" customHeight="1">
       <c r="A32" t="s">
         <v>375</v>
       </c>
@@ -8647,11 +8618,11 @@
       <c r="C32" t="s">
         <v>503</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="17" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>378</v>
       </c>
@@ -8661,11 +8632,11 @@
       <c r="C33" t="s">
         <v>503</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="17" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>381</v>
       </c>
@@ -8675,11 +8646,11 @@
       <c r="C34" t="s">
         <v>503</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="17" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="85.6" x14ac:dyDescent="0.25">
+    <row r="35" ht="85.6" customHeight="1">
       <c r="A35" t="s">
         <v>384</v>
       </c>
@@ -8689,11 +8660,11 @@
       <c r="C35" t="s">
         <v>503</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="17" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="36" ht="28.55" customHeight="1">
       <c r="A36" t="s">
         <v>387</v>
       </c>
@@ -8703,11 +8674,11 @@
       <c r="C36" t="s">
         <v>503</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="17" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -8717,11 +8688,11 @@
       <c r="C37" t="s">
         <v>503</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="17" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>180</v>
       </c>
@@ -8731,11 +8702,11 @@
       <c r="C38" t="s">
         <v>503</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="17" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>153</v>
       </c>
@@ -8745,11 +8716,11 @@
       <c r="C39" t="s">
         <v>503</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="17" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -8759,11 +8730,11 @@
       <c r="C40" t="s">
         <v>503</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="17" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>171</v>
       </c>
@@ -8773,11 +8744,11 @@
       <c r="C41" t="s">
         <v>503</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="17" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>174</v>
       </c>
@@ -8787,11 +8758,11 @@
       <c r="C42" t="s">
         <v>503</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="17" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -8801,11 +8772,11 @@
       <c r="C43" t="s">
         <v>503</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="17" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>165</v>
       </c>
@@ -8815,11 +8786,11 @@
       <c r="C44" t="s">
         <v>503</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="17" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>162</v>
       </c>
@@ -8829,11 +8800,11 @@
       <c r="C45" t="s">
         <v>503</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="17" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>128</v>
       </c>
@@ -8843,11 +8814,11 @@
       <c r="C46" t="s">
         <v>503</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="17" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>168</v>
       </c>
@@ -8861,7 +8832,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>177</v>
       </c>
@@ -8875,7 +8846,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -8889,7 +8860,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -8903,7 +8874,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>190</v>
       </c>
@@ -8913,11 +8884,11 @@
       <c r="C51" t="s">
         <v>503</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="17" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>193</v>
       </c>
@@ -8927,11 +8898,11 @@
       <c r="C52" t="s">
         <v>503</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="17" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>196</v>
       </c>
@@ -8941,11 +8912,11 @@
       <c r="C53" t="s">
         <v>503</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="17" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -8955,11 +8926,11 @@
       <c r="C54" t="s">
         <v>503</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="17" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="57.1" x14ac:dyDescent="0.25">
+    <row r="55" ht="57.1" customHeight="1">
       <c r="A55" t="s">
         <v>202</v>
       </c>
@@ -8969,11 +8940,11 @@
       <c r="C55" t="s">
         <v>503</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="17" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>205</v>
       </c>
@@ -8983,11 +8954,11 @@
       <c r="C56" t="s">
         <v>503</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="17" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>208</v>
       </c>
@@ -8997,11 +8968,11 @@
       <c r="C57" t="s">
         <v>503</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="17" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="28.55" x14ac:dyDescent="0.25">
+    <row r="58" ht="28.55" customHeight="1">
       <c r="A58" t="s">
         <v>211</v>
       </c>
@@ -9011,11 +8982,11 @@
       <c r="C58" t="s">
         <v>503</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="17" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>214</v>
       </c>
@@ -9025,11 +8996,11 @@
       <c r="C59" t="s">
         <v>503</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="17" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>225</v>
       </c>
@@ -9045,20 +9016,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="62.375" customWidth="1"/>
-    <col min="3" max="4" width="19.375" customWidth="1"/>
+    <col min="1" max="1" width="19.375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="62.375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.375" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="19.375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>389</v>
       </c>
@@ -9075,298 +9048,6 @@
   </sheetData>
   <autoFilter ref="A1:D60" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010018943E1407CCF04989863CF0F432E8B2" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="db7879c5843627d2d5018033e2f13957">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="352660e0-d3e8-47c6-9ec5-fea43b473253" xmlns:ns3="d9de82e3-6650-437c-811c-4330ac3163a7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2446b3d32c0630b69da860c4e69f999" ns2:_="" ns3:_="">
-    <xsd:import namespace="352660e0-d3e8-47c6-9ec5-fea43b473253"/>
-    <xsd:import namespace="d9de82e3-6650-437c-811c-4330ac3163a7"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="352660e0-d3e8-47c6-9ec5-fea43b473253" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d49e3c31-ed93-422f-85c6-5d6f62fb859e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d9de82e3-6650-437c-811c-4330ac3163a7" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f6c7ab44-08e3-4c86-bbfd-d550f2323352}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d9de82e3-6650-437c-811c-4330ac3163a7">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d9de82e3-6650-437c-811c-4330ac3163a7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="352660e0-d3e8-47c6-9ec5-fea43b473253">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99401450-4116-472E-9386-888FD56A9AF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="352660e0-d3e8-47c6-9ec5-fea43b473253"/>
-    <ds:schemaRef ds:uri="d9de82e3-6650-437c-811c-4330ac3163a7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4A2FCDB-4CEB-4560-BC24-5417B97B9546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E58BEAF-C168-4A50-BC01-2C2CE605BA70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d9de82e3-6650-437c-811c-4330ac3163a7"/>
-    <ds:schemaRef ds:uri="352660e0-d3e8-47c6-9ec5-fea43b473253"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>